--- a/docs/metricas-website-playbook.xlsx
+++ b/docs/metricas-website-playbook.xlsx
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="B44" s="0">
-        <v>12021</v>
+        <v>12024</v>
       </c>
       <c r="C44" s="0">
-        <v>11678</v>
+        <v>11681</v>
       </c>
       <c r="D44" s="0">
         <f>IFERROR(B44/C44,"")</f>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>12609</v>
+        <v>12612</v>
       </c>
       <c r="B48" s="0">
         <v>155</v>

--- a/docs/metricas-website-playbook.xlsx
+++ b/docs/metricas-website-playbook.xlsx
@@ -15,6 +15,7 @@
   <definedNames>
     <definedName name="GA4_Resumen_Mes">Datos_GA4!$A$6:$A$41</definedName>
     <definedName name="GA4_Resumen_Usuarios">Datos_GA4!$B$6:$B$41</definedName>
+    <definedName name="GA4_Resumen_Nuevos">Datos_GA4!$C$6:$C$41</definedName>
     <definedName name="GA4_Resumen_Sesiones">Datos_GA4!$E$6:$E$41</definedName>
     <definedName name="GA4_Resumen_Vistas">Datos_GA4!$F$6:$F$41</definedName>
     <definedName name="GA4_Disp_Categoria">Datos_GA4!$B$123:$B$158</definedName>
@@ -1069,168 +1070,270 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECURRENCIA Y RECIRCULACIÓN — las dos métricas ancla del área</t>
+          <t xml:space="preserve">LAS DOS FUENTES NO COINCIDEN — leer esto antes que cualquier cifra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métrica</t>
+          <t xml:space="preserve">Fuente</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor</t>
+          <t xml:space="preserve">Usuarios</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lectura</t>
+          <t xml:space="preserve">Vistas / lecturas</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué cuenta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lecturas por lector</t>
+          <t xml:space="preserve">GA4 (desde el 2026-08-10)</t>
         </is>
       </c>
       <c r="B14" s="0">
-        <f>IFERROR(SUM(Datos_Portal!B43:B44)/SUM(Datos_Portal!C43:C44),"")</f>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proxy de recirculación. 1.00 = nadie lee una segunda nota.</t>
+        <v>677</v>
+      </c>
+      <c r="C14" s="0">
+        <v>2032</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navegadores reales que ejecutaron JavaScript.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">% de lectores recurrentes</t>
-        </is>
-      </c>
-      <c r="B15" s="7">
-        <f>IFERROR(Datos_Portal!B48/Datos_Portal!A48,"")</f>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lectores con más de una lectura registrada.</t>
+          <t xml:space="preserve">Portal, misma ventana</t>
+        </is>
+      </c>
+      <c r="B15" s="0">
+        <v>9067</v>
+      </c>
+      <c r="C15" s="0">
+        <v>9304</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peticiones al servidor, con o sin JavaScript.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambas salen de article_reads, no de GA4: son dato de primera parte y no dependen de consentimiento de cookies de terceros.</t>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diferencia</t>
+        </is>
+      </c>
+      <c r="B16" s="0">
+        <f>IFERROR(B15/B14,"")</f>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veces que el contador propio supera a GA4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POR QUÉ NO COINCIDEN, y por qué importa. lib/bots.ts filtra sólo 14 user-agents (googlebot, bingbot, facebookexternalhit…). No incluye GPTBot, ClaudeBot, CCBot, PerplexityBot, Bytespider, AhrefsBot ni el resto. Un crawler fuera de esa lista pasa el filtro, recibe una cookie anónima, no la persiste, y en la siguiente petición se cuenta como un lector NUEVO. En los datos se ve exactamente así: lecturas ≈ lectores todos los días, es decir una sola lectura por identidad.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LO QUE FALTA INSTRUMENTAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONSECUENCIA: 'lecturas por lector' y '% de recurrencia' NO miden recirculación hoy. Miden cuánto tráfico automatizado se está contando como lectores. Se quedan abajo como diagnóstico, NO como KPI, y no deben presentarse a dirección hasta arreglar el filtro de bots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAGNÓSTICO — no son KPI todavía</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Métrica</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estado</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Usuarios, sesiones, vistas</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4 (ver Instrucciones).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Canales de adquisición</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4.</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lectura</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile vs desktop</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
-        </is>
+          <t xml:space="preserve">Lecturas por lector (propio)</t>
+        </is>
+      </c>
+      <c r="B22" s="0">
+        <f>IFERROR(SUM(Datos_Portal!B43:B44)/SUM(Datos_Portal!C43:C44),"")</f>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4.</t>
+          <t xml:space="preserve">Pegado a 1.00 porque casi cada lectura estrena identidad. Síntoma, no hallazgo.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversión website → newsletter</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
-        </is>
+          <t xml:space="preserve">% de lectores recurrentes (propio)</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>IFERROR(Datos_Portal!B48/Datos_Portal!A48,"")</f>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No existe evento de suscripción en GA4 ni tabla de suscriptores en el portal: los suscriptores viven en Substack. Hay que (a) disparar un evento GA4 en el alta y (b) exportar el total de Substack cada mes.</t>
+          <t xml:space="preserve">Mismo problema: el denominador está inflado por bots.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">% de usuarios nuevos (GA4)</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>IFERROR(INDEX(GA4_Resumen_Nuevos,1)/INDEX(GA4_Resumen_Usuarios,1),"")</f>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GA4 tampoco puede medir recurrencia aún: lleva 16 días, así que casi todos son nuevos por construcción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LO QUE FALTA INSTRUMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métrica</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuarios, sesiones, vistas</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4 (ver Instrucciones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canales de adquisición</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobile vs desktop</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pegar el export de GA4 en Datos_GA4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversión website → newsletter</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No existe evento de suscripción en GA4 ni tabla de suscriptores en el portal: los suscriptores viven en Substack. Hay que (a) disparar un evento GA4 en el alta y (b) exportar el total de Substack cada mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tiempo de lectura real</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">PENDIENTE DE INSTRUMENTACIÓN</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">El portal guarda reading_time ESTIMADO, no medido. El medido sale de GA4.</t>
         </is>
@@ -2226,14 +2329,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Datos_GA4 — hoja destino. Pegar aquí el export, sin reformatear.</t>
+          <t xml:space="preserve">Datos_GA4 — datos de la API de GA4.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VACÍA A PROPÓSITO. Esta máquina no tiene credenciales de GA4 (las cuatro claves GA4_* existen en .env.local y están en blanco), así que cualquier cifra aquí sería inventada. Los encabezados son los exactos del export de GA4 G-KVE4HF75TF. Ruta de clics por reporte: docs/metricas-website-runbook.md.</t>
+          <t xml:space="preserve">Rellenada automáticamente desde la API de GA4 el 2026-08-25 (scripts/ga4-export.ts). Se puede seguir pegando a mano debajo: las filas de la API y las pegadas son indistinguibles para las fórmulas. OJO CON EL RANGO: la propiedad G-KVE4HF75TF sólo tiene datos desde el 2026-08-10, así que cualquier mes anterior sale vacío porque no existe, no porque falte pegarlo.</t>
         </is>
       </c>
     </row>
@@ -2286,6 +2389,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B6" s="0">
+        <v>677</v>
+      </c>
+      <c r="C6" s="0">
+        <v>673</v>
+      </c>
+      <c r="D6" s="0">
+        <f>IFERROR(B6-C6,"")</f>
+      </c>
+      <c r="E6" s="0">
+        <v>1057</v>
+      </c>
+      <c r="F6" s="0">
+        <v>2032</v>
+      </c>
+      <c r="G6" s="0">
+        <v>222.5321</v>
+      </c>
+      <c r="H6" s="0">
+        <v>0.4163</v>
+      </c>
+    </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
@@ -2325,6 +2456,198 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct</t>
+        </is>
+      </c>
+      <c r="C45" s="0">
+        <v>320</v>
+      </c>
+      <c r="D45" s="0">
+        <v>191</v>
+      </c>
+      <c r="E45" s="0">
+        <v>586</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0.4813</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic Search</t>
+        </is>
+      </c>
+      <c r="C46" s="0">
+        <v>260</v>
+      </c>
+      <c r="D46" s="0">
+        <v>217</v>
+      </c>
+      <c r="E46" s="0">
+        <v>326</v>
+      </c>
+      <c r="F46" s="0">
+        <v>0.4692</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email</t>
+        </is>
+      </c>
+      <c r="C47" s="0">
+        <v>259</v>
+      </c>
+      <c r="D47" s="0">
+        <v>194</v>
+      </c>
+      <c r="E47" s="0">
+        <v>443</v>
+      </c>
+      <c r="F47" s="0">
+        <v>0.2394</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral</t>
+        </is>
+      </c>
+      <c r="C48" s="0">
+        <v>116</v>
+      </c>
+      <c r="D48" s="0">
+        <v>20</v>
+      </c>
+      <c r="E48" s="0">
+        <v>483</v>
+      </c>
+      <c r="F48" s="0">
+        <v>0.6121</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organic Social</t>
+        </is>
+      </c>
+      <c r="C49" s="0">
+        <v>77</v>
+      </c>
+      <c r="D49" s="0">
+        <v>56</v>
+      </c>
+      <c r="E49" s="0">
+        <v>99</v>
+      </c>
+      <c r="F49" s="0">
+        <v>0.3766</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unassigned</t>
+        </is>
+      </c>
+      <c r="C50" s="0">
+        <v>68</v>
+      </c>
+      <c r="D50" s="0">
+        <v>47</v>
+      </c>
+      <c r="E50" s="0">
+        <v>84</v>
+      </c>
+      <c r="F50" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-network</t>
+        </is>
+      </c>
+      <c r="C51" s="0">
+        <v>5</v>
+      </c>
+      <c r="D51" s="0">
+        <v>5</v>
+      </c>
+      <c r="E51" s="0">
+        <v>5</v>
+      </c>
+      <c r="F51" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Assistant</t>
+        </is>
+      </c>
+      <c r="C52" s="0">
+        <v>3</v>
+      </c>
+      <c r="D52" s="0">
+        <v>3</v>
+      </c>
+      <c r="E52" s="0">
+        <v>6</v>
+      </c>
+      <c r="F52" s="0">
+        <v>0.6667</v>
+      </c>
+    </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
@@ -2359,6 +2682,342 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/articulo</t>
+        </is>
+      </c>
+      <c r="C84" s="0">
+        <v>1090</v>
+      </c>
+      <c r="D84" s="0">
+        <v>490</v>
+      </c>
+      <c r="E84" s="0">
+        <v>29675</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="C85" s="0">
+        <v>715</v>
+      </c>
+      <c r="D85" s="0">
+        <v>226</v>
+      </c>
+      <c r="E85" s="0">
+        <v>12477</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/archivo</t>
+        </is>
+      </c>
+      <c r="C86" s="0">
+        <v>124</v>
+      </c>
+      <c r="D86" s="0">
+        <v>19</v>
+      </c>
+      <c r="E86" s="0">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/coberturas/lfa</t>
+        </is>
+      </c>
+      <c r="C87" s="0">
+        <v>31</v>
+      </c>
+      <c r="D87" s="0">
+        <v>7</v>
+      </c>
+      <c r="E87" s="0">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/la-lana</t>
+        </is>
+      </c>
+      <c r="C88" s="0">
+        <v>16</v>
+      </c>
+      <c r="D88" s="0">
+        <v>11</v>
+      </c>
+      <c r="E88" s="0">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/infinitas</t>
+        </is>
+      </c>
+      <c r="C89" s="0">
+        <v>14</v>
+      </c>
+      <c r="D89" s="0">
+        <v>11</v>
+      </c>
+      <c r="E89" s="0">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/noticias</t>
+        </is>
+      </c>
+      <c r="C90" s="0">
+        <v>12</v>
+      </c>
+      <c r="D90" s="0">
+        <v>9</v>
+      </c>
+      <c r="E90" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/privacidad</t>
+        </is>
+      </c>
+      <c r="C91" s="0">
+        <v>9</v>
+      </c>
+      <c r="D91" s="0">
+        <v>9</v>
+      </c>
+      <c r="E91" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/cuenta</t>
+        </is>
+      </c>
+      <c r="C92" s="0">
+        <v>6</v>
+      </c>
+      <c r="D92" s="0">
+        <v>6</v>
+      </c>
+      <c r="E92" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/futbol-business-review</t>
+        </is>
+      </c>
+      <c r="C93" s="0">
+        <v>5</v>
+      </c>
+      <c r="D93" s="0">
+        <v>4</v>
+      </c>
+      <c r="E93" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/tema</t>
+        </is>
+      </c>
+      <c r="C94" s="0">
+        <v>4</v>
+      </c>
+      <c r="D94" s="0">
+        <v>4</v>
+      </c>
+      <c r="E94" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/blog/debiera-la-liga-mx-partirse-para-lograr-la-inversio-n</t>
+        </is>
+      </c>
+      <c r="C95" s="0">
+        <v>2</v>
+      </c>
+      <c r="D95" s="0">
+        <v>2</v>
+      </c>
+      <c r="E95" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/about</t>
+        </is>
+      </c>
+      <c r="C96" s="0">
+        <v>1</v>
+      </c>
+      <c r="D96" s="0">
+        <v>1</v>
+      </c>
+      <c r="E96" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/blog/el-futuro-del-mexico-open-esta-en-juego</t>
+        </is>
+      </c>
+      <c r="C97" s="0">
+        <v>1</v>
+      </c>
+      <c r="D97" s="0">
+        <v>1</v>
+      </c>
+      <c r="E97" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/equipo</t>
+        </is>
+      </c>
+      <c r="C98" s="0">
+        <v>1</v>
+      </c>
+      <c r="D98" s="0">
+        <v>1</v>
+      </c>
+      <c r="E98" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/lfa</t>
+        </is>
+      </c>
+      <c r="C99" s="0">
+        <v>1</v>
+      </c>
+      <c r="D99" s="0">
+        <v>1</v>
+      </c>
+      <c r="E99" s="0">
+        <v>0</v>
+      </c>
+    </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
@@ -2393,6 +3052,69 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="C123" s="0">
+        <v>419</v>
+      </c>
+      <c r="D123" s="0">
+        <v>718</v>
+      </c>
+      <c r="E123" s="0">
+        <v>0.4192</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mobile</t>
+        </is>
+      </c>
+      <c r="C124" s="0">
+        <v>253</v>
+      </c>
+      <c r="D124" s="0">
+        <v>334</v>
+      </c>
+      <c r="E124" s="0">
+        <v>0.4072</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tablet</t>
+        </is>
+      </c>
+      <c r="C125" s="0">
+        <v>5</v>
+      </c>
+      <c r="D125" s="0">
+        <v>7</v>
+      </c>
+      <c r="E125" s="0">
+        <v>0.4286</v>
+      </c>
+    </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
@@ -2425,6 +3147,312 @@
         <is>
           <t xml:space="preserve">Sesiones con el evento</t>
         </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">page_view</t>
+        </is>
+      </c>
+      <c r="C162" s="0">
+        <v>2032</v>
+      </c>
+      <c r="D162" s="0">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">user_engagement</t>
+        </is>
+      </c>
+      <c r="C163" s="0">
+        <v>1050</v>
+      </c>
+      <c r="D163" s="0">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">session_start</t>
+        </is>
+      </c>
+      <c r="C164" s="0">
+        <v>1046</v>
+      </c>
+      <c r="D164" s="0">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scroll_depth</t>
+        </is>
+      </c>
+      <c r="C165" s="0">
+        <v>704</v>
+      </c>
+      <c r="D165" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">first_visit</t>
+        </is>
+      </c>
+      <c r="C166" s="0">
+        <v>673</v>
+      </c>
+      <c r="D166" s="0">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scroll</t>
+        </is>
+      </c>
+      <c r="C167" s="0">
+        <v>310</v>
+      </c>
+      <c r="D167" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">article_read_complete</t>
+        </is>
+      </c>
+      <c r="C168" s="0">
+        <v>78</v>
+      </c>
+      <c r="D168" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">click</t>
+        </is>
+      </c>
+      <c r="C169" s="0">
+        <v>34</v>
+      </c>
+      <c r="D169" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email_wall_view</t>
+        </is>
+      </c>
+      <c r="C170" s="0">
+        <v>24</v>
+      </c>
+      <c r="D170" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">outbound_click</t>
+        </is>
+      </c>
+      <c r="C171" s="0">
+        <v>14</v>
+      </c>
+      <c r="D171" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">product_hub_visit</t>
+        </is>
+      </c>
+      <c r="C172" s="0">
+        <v>12</v>
+      </c>
+      <c r="D172" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">form_start</t>
+        </is>
+      </c>
+      <c r="C173" s="0">
+        <v>5</v>
+      </c>
+      <c r="D173" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_visit</t>
+        </is>
+      </c>
+      <c r="C174" s="0">
+        <v>4</v>
+      </c>
+      <c r="D174" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">form_submit</t>
+        </is>
+      </c>
+      <c r="C175" s="0">
+        <v>2</v>
+      </c>
+      <c r="D175" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email_wall_cta</t>
+        </is>
+      </c>
+      <c r="C176" s="0">
+        <v>1</v>
+      </c>
+      <c r="D176" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newsletter_signup</t>
+        </is>
+      </c>
+      <c r="C177" s="0">
+        <v>1</v>
+      </c>
+      <c r="D177" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08</t>
+        </is>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tag_nav_click</t>
+        </is>
+      </c>
+      <c r="C178" s="0">
+        <v>1</v>
+      </c>
+      <c r="D178" s="0">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3226,10 +4254,10 @@
         </is>
       </c>
       <c r="B44" s="0">
-        <v>12024</v>
+        <v>12037</v>
       </c>
       <c r="C44" s="0">
-        <v>11681</v>
+        <v>11694</v>
       </c>
       <c r="D44" s="0">
         <f>IFERROR(B44/C44,"")</f>
@@ -3266,7 +4294,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>12612</v>
+        <v>12625</v>
       </c>
       <c r="B48" s="0">
         <v>155</v>
